--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5604.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5604.xlsx
@@ -1333,6 +1333,12 @@
       <c r="D15" t="n">
         <v>0.78</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.33</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>5604-02-02-02-FG</t>
@@ -1345,12 +1351,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1378,6 +1384,12 @@
       <c r="D16" t="n">
         <v>1.59</v>
       </c>
+      <c r="G16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.91</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>5604-12-12-12-FG</t>
@@ -1390,12 +1402,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1423,6 +1435,12 @@
       <c r="D17" t="n">
         <v>1.97</v>
       </c>
+      <c r="G17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.14</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>5604-16-16-16-FG</t>
@@ -1435,12 +1453,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1468,6 +1486,12 @@
       <c r="D18" t="n">
         <v>2.38</v>
       </c>
+      <c r="G18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.48</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>5604-20-20-20-FG</t>
@@ -1480,12 +1504,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1513,6 +1537,12 @@
       <c r="D19" t="n">
         <v>3</v>
       </c>
+      <c r="G19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.2</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>5604-32-32-32-FG</t>
@@ -1525,12 +1555,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5604-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5604-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5604.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5604.xlsx
@@ -1330,15 +1330,36 @@
           <t>5604-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.66</v>
+      </c>
       <c r="D15" t="n">
         <v>0.78</v>
       </c>
+      <c r="E15" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.188</v>
+      </c>
       <c r="G15" t="n">
         <v>0.33</v>
       </c>
       <c r="H15" t="n">
         <v>0.33</v>
       </c>
+      <c r="I15" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.405</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>5604-02-02-02-FG</t>
@@ -1346,17 +1367,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, N1_1@DRIVE, N1_2@DRIVE, W@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N, N1_1@DRIVE=N1, N1_2@DRIVE=N2, W@HEX=Y, D@BORE=A3D, THDMAJ_A1@DRIVE=THD1, THDMAJ_A2@DRIVE=THD1, THDMAJ_A3@DRIVE=THD3; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1381,15 +1402,36 @@
           <t>5604-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.36</v>
+      </c>
       <c r="D16" t="n">
         <v>1.59</v>
       </c>
+      <c r="E16" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.719</v>
+      </c>
       <c r="G16" t="n">
         <v>0.91</v>
       </c>
       <c r="H16" t="n">
         <v>0.91</v>
       </c>
+      <c r="I16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.05</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>5604-12-12-12-FG</t>
@@ -1397,17 +1439,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, N1_1@DRIVE, N1_2@DRIVE, W@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N, N1_1@DRIVE=N1, N1_2@DRIVE=N2, W@HEX=Y, D@BORE=A3D, THDMAJ_A1@DRIVE=THD1, THDMAJ_A2@DRIVE=THD1, THDMAJ_A3@DRIVE=THD3; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1432,15 +1474,36 @@
           <t>5604-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.62</v>
+      </c>
       <c r="D17" t="n">
         <v>1.97</v>
       </c>
+      <c r="E17" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9379999999999999</v>
+      </c>
       <c r="G17" t="n">
         <v>1.14</v>
       </c>
       <c r="H17" t="n">
         <v>1.14</v>
       </c>
+      <c r="I17" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.315</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>5604-16-16-16-FG</t>
@@ -1448,17 +1511,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, N1_1@DRIVE, N1_2@DRIVE, W@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N, N1_1@DRIVE=N1, N1_2@DRIVE=N2, W@HEX=Y, D@BORE=A3D, THDMAJ_A1@DRIVE=THD1, THDMAJ_A2@DRIVE=THD1, THDMAJ_A3@DRIVE=THD3; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1483,15 +1546,36 @@
           <t>5604-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.7</v>
+      </c>
       <c r="D18" t="n">
         <v>2.38</v>
       </c>
+      <c r="E18" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G18" t="n">
         <v>1.48</v>
       </c>
       <c r="H18" t="n">
         <v>1.48</v>
       </c>
+      <c r="I18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.66</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>5604-20-20-20-FG</t>
@@ -1499,17 +1583,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, N1_1@DRIVE, N1_2@DRIVE, W@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5604-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5604-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5604-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N, N1_1@DRIVE=N1, N1_2@DRIVE=N2, W@HEX=Y, D@BORE=A3D, THDMAJ_A1@DRIVE=THD1, THDMAJ_A2@DRIVE=THD1, THDMAJ_A3@DRIVE=THD3; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1534,15 +1618,36 @@
           <t>5604-32-32-32-FG</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.39</v>
+      </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
+      <c r="E19" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.938</v>
+      </c>
       <c r="G19" t="n">
         <v>2.2</v>
       </c>
       <c r="H19" t="n">
         <v>2.2</v>
       </c>
+      <c r="I19" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.375</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>5604-32-32-32-FG</t>
@@ -1550,17 +1655,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, N1_1@DRIVE, N1_2@DRIVE, W@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5604-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5604-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N, N1_1@DRIVE=N1, N1_2@DRIVE=N2, W@HEX=Y, D@BORE=A3D, THDMAJ_A1@DRIVE=THD1, THDMAJ_A2@DRIVE=THD1, THDMAJ_A3@DRIVE=THD3; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
